--- a/docs/feishu-import/花名册 2026-04-29_152534.xlsx
+++ b/docs/feishu-import/花名册 2026-04-29_152534.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="在职人员" sheetId="1" r:id="rId1"/>
-    <sheet name="dropList" sheetId="2" r:id="rId5" state="hidden"/>
+    <sheet name="dropList" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="500">
   <si>
     <t>姓名</t>
   </si>
@@ -158,6 +158,165 @@
     <t>备注</t>
   </si>
   <si>
+    <t>叶泽奇</t>
+  </si>
+  <si>
+    <t>保密</t>
+  </si>
+  <si>
+    <t>+86 15867443257</t>
+  </si>
+  <si>
+    <t>yezeqi@crowncad.com</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>在职</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/基础研发中心/基础研发四部</t>
+  </si>
+  <si>
+    <t>正式</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>0 月</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ee3ef492</t>
+  </si>
+  <si>
+    <t>戴佳伟</t>
+  </si>
+  <si>
+    <t>+86 13964113374</t>
+  </si>
+  <si>
+    <t>daijiawei@crowncad.com</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/基础研发中心/基础研发四部,山东山大华天软件股份有限公司/山东华云三维科技有限公司/基础研发中心</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>78fe8e9b</t>
+  </si>
+  <si>
+    <t>于善鹏</t>
+  </si>
+  <si>
+    <t>+86 13964112234</t>
+  </si>
+  <si>
+    <t>yushanpeng@crowncad.com</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/产品研发中心/产品研发一部/六组</t>
+  </si>
+  <si>
+    <t>276b33cd</t>
+  </si>
+  <si>
+    <t>陈杰斌</t>
+  </si>
+  <si>
+    <t>+86 13964885524</t>
+  </si>
+  <si>
+    <t>chenjiebin@crowncad.com</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/产品研发中心/产品研发一部/四组</t>
+  </si>
+  <si>
+    <t>cab11466</t>
+  </si>
+  <si>
+    <t>+86 13964882265</t>
+  </si>
+  <si>
+    <t>daijiawei2@crowncad.com</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>464872c2</t>
+  </si>
+  <si>
+    <t>用户725015</t>
+  </si>
+  <si>
+    <t>+86 15850553970</t>
+  </si>
+  <si>
+    <t>yonghu@crowncad.com</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/产品研发中心/产品研发三部</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>5f4ad879</t>
+  </si>
+  <si>
+    <t>侯国玉</t>
+  </si>
+  <si>
+    <t>+86 12394558834</t>
+  </si>
+  <si>
+    <t>houguoyu@crowncad.com</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>山东山大华天软件股份有限公司/山东华云三维科技有限公司/产品研发中心/产品研发三部/一组</t>
+  </si>
+  <si>
+    <t>外包</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>1 月</t>
+  </si>
+  <si>
+    <t>无需转正</t>
+  </si>
+  <si>
+    <t>e62d4g7c</t>
+  </si>
+  <si>
     <t>gender</t>
   </si>
   <si>
@@ -167,9 +326,6 @@
     <t>女</t>
   </si>
   <si>
-    <t>保密</t>
-  </si>
-  <si>
     <t>其他</t>
   </si>
   <si>
@@ -1229,9 +1385,6 @@
     <t>employee_status</t>
   </si>
   <si>
-    <t>在职</t>
-  </si>
-  <si>
     <t>待转正</t>
   </si>
   <si>
@@ -1250,15 +1403,9 @@
     <t>employee_type</t>
   </si>
   <si>
-    <t>正式</t>
-  </si>
-  <si>
     <t>实习</t>
   </si>
   <si>
-    <t>外包</t>
-  </si>
-  <si>
     <t>劳务</t>
   </si>
   <si>
@@ -1367,176 +1514,199 @@
     <t>conversion_status</t>
   </si>
   <si>
-    <t>无需转正</t>
-  </si>
-  <si>
     <t>已转正</t>
-  </si>
-  <si>
-    <t>叶泽奇</t>
-  </si>
-  <si>
-    <t>+86 15867443257</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>基础开发部门</t>
-  </si>
-  <si>
-    <t>用户725015的组织/开发部门/基础开发部门</t>
-  </si>
-  <si>
-    <t>开发部门</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>0 月</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>ee3ef492</t>
-  </si>
-  <si>
-    <t>戴佳伟</t>
-  </si>
-  <si>
-    <t>+86 13964113374</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>效能平台</t>
-  </si>
-  <si>
-    <t>用户725015的组织/开发部门/平台开发部门/效能平台</t>
-  </si>
-  <si>
-    <t>平台开发部门</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>78fe8e9b</t>
-  </si>
-  <si>
-    <t>于善鹏</t>
-  </si>
-  <si>
-    <t>+86 13964112234</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>用户725015的组织/开发部门</t>
-  </si>
-  <si>
-    <t>276b33cd</t>
-  </si>
-  <si>
-    <t>陈杰斌</t>
-  </si>
-  <si>
-    <t>+86 13964885524</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>cab11466</t>
-  </si>
-  <si>
-    <t>+86 13964882265</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>464872c2</t>
-  </si>
-  <si>
-    <t>用户725015</t>
-  </si>
-  <si>
-    <t>+86 15850553970</t>
-  </si>
-  <si>
-    <t>用户725015的组织</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>5f4ad879</t>
-  </si>
-  <si>
-    <t>侯国玉</t>
-  </si>
-  <si>
-    <t>+86 12394558834</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>基础开发一部</t>
-  </si>
-  <si>
-    <t>用户725015的组织/开发部门/基础开发部门/基础开发一部</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>1 月</t>
-  </si>
-  <si>
-    <t>e62d4g7c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1546,10 +1716,191 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1587,27 +1938,323 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="10" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1654,7 +2301,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1689,7 +2336,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1863,2545 +2510,2564 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelRow="7"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="1" width="13"/>
-    <col customWidth="true" max="3" min="2" style="1" width="7"/>
-    <col customWidth="true" max="4" min="4" style="1" width="16"/>
-    <col customWidth="true" max="5" min="5" style="1" width="13"/>
-    <col customWidth="true" max="6" min="6" style="3" width="13"/>
-    <col customWidth="true" max="7" min="7" style="1" width="7"/>
-    <col customWidth="true" max="8" min="8" style="1" width="19"/>
-    <col customWidth="true" max="9" min="9" style="1" width="7"/>
-    <col customWidth="true" max="10" min="10" style="1" width="13"/>
-    <col customWidth="true" max="11" min="11" style="1" width="16"/>
-    <col customWidth="true" max="12" min="12" style="1" width="7"/>
-    <col customWidth="true" max="13" min="13" style="1" width="16"/>
-    <col customWidth="true" max="15" min="14" style="1" width="13"/>
-    <col customWidth="true" max="16" min="16" style="3" width="25"/>
-    <col customWidth="true" max="17" min="17" style="1" width="7"/>
-    <col customWidth="true" max="18" min="18" style="1" width="13"/>
-    <col customWidth="true" max="19" min="19" style="1" width="16"/>
-    <col customWidth="true" max="20" min="20" style="1" width="7"/>
-    <col customWidth="true" max="22" min="21" style="1" width="13"/>
-    <col customWidth="true" max="25" min="23" style="1" width="7"/>
-    <col customWidth="true" max="26" min="26" style="1" width="22"/>
-    <col customWidth="true" max="27" min="27" style="1" width="73"/>
-    <col customWidth="true" max="28" min="28" style="1" width="13"/>
-    <col customWidth="true" max="30" min="29" style="1" width="19"/>
-    <col customWidth="true" max="35" min="31" style="1" width="13"/>
-    <col customWidth="true" max="36" min="36" style="1" width="10"/>
-    <col customWidth="true" max="37" min="37" style="1" width="16"/>
-    <col customWidth="true" max="38" min="38" style="1" width="13"/>
-    <col customWidth="true" max="39" min="39" style="1" width="7"/>
-    <col customWidth="true" max="40" min="40" style="3" width="13"/>
-    <col customWidth="true" max="41" min="41" style="1" width="7"/>
-    <col customWidth="true" max="42" min="42" style="1" width="19"/>
-    <col customWidth="true" max="43" min="43" style="3" width="13"/>
-    <col customWidth="true" max="44" min="44" style="1" width="13"/>
-    <col customWidth="true" max="45" min="45" style="1" width="7"/>
-    <col customWidth="true" max="46" min="46" style="1" width="10"/>
-    <col customWidth="true" max="47" min="47" style="1" width="7"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="3" width="7" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7" style="1" customWidth="1"/>
+    <col min="21" max="22" width="13" style="1" customWidth="1"/>
+    <col min="23" max="25" width="7" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22" style="1" customWidth="1"/>
+    <col min="27" max="27" width="73" style="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" customWidth="1"/>
+    <col min="29" max="30" width="19" style="1" customWidth="1"/>
+    <col min="31" max="35" width="13" style="1" customWidth="1"/>
+    <col min="36" max="36" width="10" style="1" customWidth="1"/>
+    <col min="37" max="37" width="16" style="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" customWidth="1"/>
+    <col min="39" max="39" width="7" style="1" customWidth="1"/>
+    <col min="40" max="40" width="13" style="2" customWidth="1"/>
+    <col min="41" max="41" width="7" style="1" customWidth="1"/>
+    <col min="42" max="42" width="19" style="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="2" customWidth="1"/>
+    <col min="44" max="44" width="13" style="1" customWidth="1"/>
+    <col min="45" max="45" width="7" style="1" customWidth="1"/>
+    <col min="46" max="46" width="10" style="1" customWidth="1"/>
+    <col min="47" max="47" width="7" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:47">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="31.5" spans="1:47">
       <c r="A2" s="1" t="s">
-        <v>452</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>454</v>
+        <v>51</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>455</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
       <c r="AI2" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN2" s="3" t="s">
-        <v>459</v>
+        <v>55</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>462</v>
+        <v>59</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="31.5" spans="1:47">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>464</v>
+        <v>61</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>465</v>
+        <v>63</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>466</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
       <c r="AI3" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN3" s="3" t="s">
-        <v>469</v>
+        <v>55</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>470</v>
+        <v>66</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="31.5" spans="1:47">
       <c r="A4" s="1" t="s">
-        <v>471</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>472</v>
+        <v>68</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>473</v>
+        <v>70</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>457</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" s="1"/>
       <c r="AI4" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN4" s="3" t="s">
-        <v>469</v>
+        <v>55</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AO4" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT4" s="1" t="s">
-        <v>475</v>
+        <v>72</v>
       </c>
       <c r="AU4" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="31.5" spans="1:47">
       <c r="A5" s="1" t="s">
-        <v>476</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>477</v>
+        <v>74</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>478</v>
+        <v>76</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>455</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
       <c r="AI5" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN5" s="3" t="s">
-        <v>469</v>
+        <v>55</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="AU5" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="31.5" spans="1:47">
       <c r="A6" s="1" t="s">
-        <v>463</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>480</v>
+        <v>79</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>457</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB6" s="1"/>
       <c r="AI6" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN6" s="3" t="s">
-        <v>482</v>
+        <v>55</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>483</v>
+        <v>83</v>
       </c>
       <c r="AU6" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="31.5" spans="1:47">
       <c r="A7" s="1" t="s">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>485</v>
+        <v>85</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>486</v>
+        <v>52</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>487</v>
+        <v>55</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>460</v>
+        <v>57</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>488</v>
+        <v>89</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="31.5" spans="1:47">
       <c r="A8" s="1" t="s">
-        <v>489</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>490</v>
+        <v>91</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>491</v>
+        <v>93</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>492</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
       <c r="AI8" s="1" t="s">
-        <v>413</v>
+        <v>95</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AN8" s="3" t="s">
-        <v>494</v>
+        <v>55</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>495</v>
+        <v>97</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="AR8" s="1" t="s">
-        <v>450</v>
+        <v>98</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>496</v>
+        <v>99</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="C2:C5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="H2:H5001">
+      <formula1>dropList!$A$4:$IA$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="C2:C5001">
       <formula1>dropList!$A$2:$D$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="H2:H5001" type="list">
-      <formula1>dropList!$A$4:$IA$4</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="L2:L5001">
+      <formula1>dropList!$A$10:$AH$10</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="I2:I5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="I2:I5001">
       <formula1>dropList!$A$6:$BE$6</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="J2:J5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="J2:J5001">
       <formula1>dropList!$A$8:$D$8</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="L2:L5001" type="list">
-      <formula1>dropList!$A$10:$AH$10</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="U2:U5001">
+      <formula1>dropList!$A$16:$F$16</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="N2:N5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="N2:N5001">
       <formula1>dropList!$A$12:$N$12</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="O2:O5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="O2:O5001">
       <formula1>dropList!$A$14:$D$14</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="U2:U5001" type="list">
-      <formula1>dropList!$A$16:$F$16</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="AI2:AI5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="AI2:AI5001">
       <formula1>dropList!$A$18:$E$18</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="AK2:AK5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="AK2:AK5001">
       <formula1>dropList!$A$20:$IP$20</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" error="系统中不存在该选项" errorStyle="stop" errorTitle="错误提示" showErrorMessage="true" sqref="AR2:AR5001" type="list">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="错误提示" error="系统中不存在该选项" sqref="AR2:AR5001">
       <formula1>dropList!$A$22:$C$22</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="yezeqi@crowncad.com"/>
+    <hyperlink ref="E3" r:id="rId2" display="daijiawei@crowncad.com"/>
+    <hyperlink ref="E4" r:id="rId3" display="yushanpeng@crowncad.com"/>
+    <hyperlink ref="E5" r:id="rId4" display="chenjiebin@crowncad.com"/>
+    <hyperlink ref="E6" r:id="rId5" display="daijiawei2@crowncad.com"/>
+    <hyperlink ref="E7" r:id="rId6" display="yonghu@crowncad.com"/>
+    <hyperlink ref="E8" r:id="rId7" display="houguoyu@crowncad.com"/>
+    <hyperlink ref="V2" r:id="rId1" display="yezeqi@crowncad.com"/>
+    <hyperlink ref="V3" r:id="rId2" display="daijiawei@crowncad.com"/>
+    <hyperlink ref="V4" r:id="rId3" display="yushanpeng@crowncad.com"/>
+    <hyperlink ref="V5" r:id="rId4" display="chenjiebin@crowncad.com"/>
+    <hyperlink ref="V6" r:id="rId5" display="daijiawei2@crowncad.com"/>
+    <hyperlink ref="V7" r:id="rId6" display="yonghu@crowncad.com"/>
+    <hyperlink ref="V8" r:id="rId7" display="houguoyu@crowncad.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:IP22"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1">
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:235">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="M4" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="O4" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="P4" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="R4" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="S4" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="T4" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="U4" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="V4" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="W4" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="X4" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="Y4" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="Z4" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AC4" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AD4" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AE4" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="AF4" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AG4" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AH4" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="AI4" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="AJ4" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="AK4" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="AL4" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="AM4" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="AN4" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="AO4" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="AP4" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="AQ4" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="AR4" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="AS4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="AT4" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="AU4" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="AV4" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="AW4" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="AX4" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="AY4" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="AZ4" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="BA4" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="BB4" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="BC4" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="BD4" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="BE4" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="BF4" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="BG4" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="BH4" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="BI4" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="BJ4" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="BK4" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="BL4" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="BM4" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="BN4" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="BO4" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="BP4" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="BQ4" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="BR4" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="BS4" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="BT4" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="BU4" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="BV4" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="BW4" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="BX4" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="BY4" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="BZ4" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="CA4" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="CB4" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="CC4" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="CD4" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="CE4" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="CF4" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="CG4" t="s">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="CH4" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="CI4" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="CJ4" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="CK4" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="CL4" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="CM4" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="CN4" t="s">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="CO4" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="CP4" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="CQ4" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="CR4" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="CS4" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="CT4" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="CU4" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="CV4" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="CW4" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="CX4" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="CY4" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="CZ4" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="DA4" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="DB4" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="DC4" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="DD4" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="DE4" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="DF4" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="DG4" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="DH4" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="DI4" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="DJ4" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="DK4" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="DL4" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="DM4" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="DN4" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="DO4" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="DP4" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="DQ4" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="DR4" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="DS4" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="DT4" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="DU4" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="DV4" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="DW4" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="DX4" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="DY4" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="DZ4" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="EA4" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="EB4" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="EC4" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="ED4" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="EE4" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="EF4" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="EG4" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="EH4" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="EI4" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="EJ4" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="EK4" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="EL4" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="EM4" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="EN4" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="EO4" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="EP4" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="EQ4" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="ER4" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="ES4" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="ET4" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="EU4" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="EV4" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="EW4" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="EX4" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="EY4" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="EZ4" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="FA4" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="FB4" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="FC4" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="FD4" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="FE4" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="FF4" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="FG4" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="FH4" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="FI4" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="FJ4" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="FK4" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="FL4" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="FM4" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="FN4" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="FO4" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="FP4" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="FQ4" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="FR4" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="FS4" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="FT4" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="FU4" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="FV4" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="FW4" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="FX4" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="FY4" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="FZ4" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="GA4" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="GB4" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="GC4" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="GD4" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="GE4" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="GF4" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="GG4" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="GH4" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="GI4" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="GJ4" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="GK4" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="GL4" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="GM4" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="GN4" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="GO4" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="GP4" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="GQ4" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="GR4" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="GS4" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="GT4" t="s">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="GU4" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="GV4" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="GW4" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="GX4" t="s">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="GY4" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="GZ4" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="HA4" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="HB4" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="HC4" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="HD4" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="HE4" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="HF4" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="HG4" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="HH4" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="HI4" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="HJ4" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="HK4" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="HL4" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="HM4" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="HN4" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="HO4" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="HP4" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="HQ4" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="HR4" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="HS4" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="HT4" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="HU4" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="HV4" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="HW4" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="HX4" t="s">
-        <v>284</v>
+        <v>336</v>
       </c>
       <c r="HY4" t="s">
-        <v>285</v>
+        <v>337</v>
       </c>
       <c r="HZ4" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="IA4" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>340</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:57">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>344</v>
       </c>
       <c r="E6" t="s">
-        <v>293</v>
+        <v>345</v>
       </c>
       <c r="F6" t="s">
-        <v>294</v>
+        <v>346</v>
       </c>
       <c r="G6" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
       <c r="H6" t="s">
-        <v>296</v>
+        <v>348</v>
       </c>
       <c r="I6" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="J6" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="K6" t="s">
-        <v>299</v>
+        <v>351</v>
       </c>
       <c r="L6" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="M6" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="N6" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="O6" t="s">
-        <v>303</v>
+        <v>355</v>
       </c>
       <c r="P6" t="s">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="Q6" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="R6" t="s">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="S6" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="T6" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="U6" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="V6" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="W6" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="X6" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="Y6" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="Z6" t="s">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="AA6" t="s">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="AB6" t="s">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="AC6" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="AD6" t="s">
-        <v>318</v>
+        <v>370</v>
       </c>
       <c r="AE6" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="AF6" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="AG6" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="AH6" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="AI6" t="s">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="AJ6" t="s">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="AK6" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="AL6" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="AM6" t="s">
-        <v>327</v>
+        <v>379</v>
       </c>
       <c r="AN6" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="AO6" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="AP6" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="AQ6" t="s">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="AR6" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="AS6" t="s">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="AT6" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="AU6" t="s">
-        <v>335</v>
+        <v>387</v>
       </c>
       <c r="AV6" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="AW6" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="AX6" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="AY6" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="AZ6" t="s">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="BA6" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="BB6" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="BC6" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="BD6" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="BE6" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>346</v>
+        <v>398</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>351</v>
+        <v>403</v>
       </c>
       <c r="B10" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="D10" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="F10" t="s">
-        <v>356</v>
+        <v>408</v>
       </c>
       <c r="G10" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="H10" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="I10" t="s">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="J10" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="K10" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="L10" t="s">
-        <v>362</v>
+        <v>414</v>
       </c>
       <c r="M10" t="s">
-        <v>363</v>
+        <v>415</v>
       </c>
       <c r="N10" t="s">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="O10" t="s">
-        <v>365</v>
+        <v>417</v>
       </c>
       <c r="P10" t="s">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="Q10" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="R10" t="s">
-        <v>368</v>
+        <v>420</v>
       </c>
       <c r="S10" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="T10" t="s">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="U10" t="s">
-        <v>371</v>
+        <v>423</v>
       </c>
       <c r="V10" t="s">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="W10" t="s">
-        <v>373</v>
+        <v>425</v>
       </c>
       <c r="X10" t="s">
-        <v>374</v>
+        <v>426</v>
       </c>
       <c r="Y10" t="s">
-        <v>375</v>
+        <v>427</v>
       </c>
       <c r="Z10" t="s">
-        <v>376</v>
+        <v>428</v>
       </c>
       <c r="AA10" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="AB10" t="s">
-        <v>378</v>
+        <v>430</v>
       </c>
       <c r="AC10" t="s">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="AD10" t="s">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="AE10" t="s">
-        <v>381</v>
+        <v>433</v>
       </c>
       <c r="AF10" t="s">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="AG10" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="AH10" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>384</v>
+        <v>436</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>385</v>
+        <v>437</v>
       </c>
       <c r="B12" t="s">
-        <v>386</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="D12" t="s">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="E12" t="s">
-        <v>389</v>
+        <v>441</v>
       </c>
       <c r="F12" t="s">
-        <v>390</v>
+        <v>442</v>
       </c>
       <c r="G12" t="s">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="H12" t="s">
-        <v>392</v>
+        <v>444</v>
       </c>
       <c r="I12" t="s">
-        <v>393</v>
+        <v>445</v>
       </c>
       <c r="J12" t="s">
-        <v>394</v>
+        <v>446</v>
       </c>
       <c r="K12" t="s">
-        <v>395</v>
+        <v>447</v>
       </c>
       <c r="L12" t="s">
-        <v>396</v>
+        <v>448</v>
       </c>
       <c r="M12" t="s">
-        <v>397</v>
+        <v>449</v>
       </c>
       <c r="N12" t="s">
-        <v>398</v>
+        <v>450</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>399</v>
+        <v>451</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>453</v>
       </c>
       <c r="C14" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>403</v>
+        <v>455</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>404</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="C16" t="s">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="D16" t="s">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="F16" t="s">
-        <v>409</v>
+        <v>460</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>410</v>
+        <v>461</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="C18" t="s">
-        <v>413</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>463</v>
       </c>
       <c r="E18" t="s">
-        <v>415</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>250</v>
       </c>
       <c r="B19" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:250">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="K20" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="L20" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="M20" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="N20" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="O20" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="P20" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="Q20" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="R20" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="S20" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="T20" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="U20" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="V20" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="W20" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="X20" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="Y20" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="AA20" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="AB20" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AC20" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AD20" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="AE20" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="AF20" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="AI20" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="AJ20" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="AL20" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="AM20" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="AN20" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="AO20" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="AP20" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="AQ20" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="AR20" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="AS20" t="s">
-        <v>419</v>
+        <v>468</v>
       </c>
       <c r="AT20" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="AU20" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="AV20" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="AW20" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="AX20" t="s">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="AY20" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="AZ20" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="BA20" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="BB20" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="BC20" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="BD20" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="BE20" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="BF20" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="BG20" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="BH20" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="BI20" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="BJ20" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="BK20" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="BL20" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="BM20" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="BN20" t="s">
-        <v>422</v>
+        <v>471</v>
       </c>
       <c r="BO20" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="BP20" t="s">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="BQ20" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="BR20" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="BS20" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="BT20" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="BU20" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="BV20" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="BW20" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="BX20" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="BY20" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="BZ20" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="CA20" t="s">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="CB20" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="CC20" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="CD20" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="CE20" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="CF20" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="CG20" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="CH20" t="s">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="CI20" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="CJ20" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="CK20" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="CL20" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="CM20" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="CN20" t="s">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="CO20" t="s">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="CP20" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="CQ20" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="CR20" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="CS20" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="CT20" t="s">
-        <v>149</v>
+        <v>201</v>
       </c>
       <c r="CU20" t="s">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="CV20" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="CW20" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="CX20" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="CY20" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="CZ20" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="DA20" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="DB20" t="s">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="DC20" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="DD20" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="DE20" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="DF20" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="DG20" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="DH20" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="DI20" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="DJ20" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="DK20" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="DL20" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="DM20" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="DN20" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="DO20" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="DP20" t="s">
-        <v>424</v>
+        <v>473</v>
       </c>
       <c r="DQ20" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="DR20" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="DS20" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="DT20" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="DU20" t="s">
-        <v>425</v>
+        <v>474</v>
       </c>
       <c r="DV20" t="s">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="DW20" t="s">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="DX20" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="DY20" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="DZ20" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="EA20" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="EB20" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="EC20" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="ED20" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="EE20" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="EF20" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="EG20" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="EH20" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="EI20" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="EJ20" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="EK20" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="EL20" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="EM20" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="EN20" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="EO20" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="EP20" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="EQ20" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="ER20" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="ES20" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="ET20" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="EU20" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="EV20" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="EW20" t="s">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="EX20" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="EY20" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="EZ20" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="FA20" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="FB20" t="s">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="FC20" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="FD20" t="s">
-        <v>431</v>
+        <v>480</v>
       </c>
       <c r="FE20" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="FF20" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="FG20" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="FH20" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="FI20" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="FJ20" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="FK20" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="FL20" t="s">
-        <v>432</v>
+        <v>481</v>
       </c>
       <c r="FM20" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="FN20" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="FO20" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="FP20" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="FQ20" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="FR20" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="FS20" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="FT20" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="FU20" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="FV20" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="FW20" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="FX20" t="s">
-        <v>433</v>
+        <v>482</v>
       </c>
       <c r="FY20" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="FZ20" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="GA20" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="GB20" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="GC20" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="GD20" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="GE20" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="GF20" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="GG20" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="GH20" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="GI20" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="GJ20" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="GK20" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="GL20" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="GM20" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="GN20" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="GO20" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="GP20" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="GQ20" t="s">
-        <v>434</v>
+        <v>483</v>
       </c>
       <c r="GR20" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="GS20" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="GT20" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="GU20" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="GV20" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
       <c r="GW20" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="GX20" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="GY20" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="GZ20" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="HA20" t="s">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="HB20" t="s">
-        <v>253</v>
+        <v>305</v>
       </c>
       <c r="HC20" t="s">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="HD20" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="HE20" t="s">
-        <v>436</v>
+        <v>485</v>
       </c>
       <c r="HF20" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="HG20" t="s">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="HH20" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="HI20" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="HJ20" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="HK20" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="HL20" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="HM20" t="s">
-        <v>437</v>
+        <v>486</v>
       </c>
       <c r="HN20" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="HO20" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="HP20" t="s">
-        <v>438</v>
+        <v>487</v>
       </c>
       <c r="HQ20" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="HR20" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="HS20" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="HT20" t="s">
-        <v>439</v>
+        <v>488</v>
       </c>
       <c r="HU20" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="HV20" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="HW20" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="HX20" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="HY20" t="s">
-        <v>441</v>
+        <v>490</v>
       </c>
       <c r="HZ20" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="IA20" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="IB20" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="IC20" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="ID20" t="s">
-        <v>443</v>
+        <v>492</v>
       </c>
       <c r="IE20" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="IF20" t="s">
-        <v>444</v>
+        <v>493</v>
       </c>
       <c r="IG20" t="s">
-        <v>445</v>
+        <v>494</v>
       </c>
       <c r="IH20" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="II20" t="s">
-        <v>446</v>
+        <v>495</v>
       </c>
       <c r="IJ20" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="IK20" t="s">
-        <v>283</v>
+        <v>335</v>
       </c>
       <c r="IL20" t="s">
-        <v>447</v>
+        <v>496</v>
       </c>
       <c r="IM20" t="s">
-        <v>285</v>
+        <v>337</v>
       </c>
       <c r="IN20" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="IO20" t="s">
-        <v>448</v>
+        <v>497</v>
       </c>
       <c r="IP20" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>449</v>
+        <v>498</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>450</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="C22" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/feishu-import/花名册 2026-04-29_152534.xlsx
+++ b/docs/feishu-import/花名册 2026-04-29_152534.xlsx
@@ -2726,8 +2726,6 @@
       <c r="AA2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
       <c r="AI2" s="1" t="s">
         <v>54</v>
       </c>
@@ -2775,9 +2773,6 @@
       <c r="AA3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
       <c r="AI3" s="1" t="s">
         <v>54</v>
       </c>
@@ -2825,7 +2820,6 @@
       <c r="AA4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="AB4" s="1"/>
       <c r="AI4" s="1" t="s">
         <v>54</v>
       </c>
@@ -2873,8 +2867,6 @@
       <c r="AA5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
       <c r="AI5" s="1" t="s">
         <v>54</v>
       </c>
@@ -2922,7 +2914,6 @@
       <c r="AA6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AB6" s="1"/>
       <c r="AI6" s="1" t="s">
         <v>54</v>
       </c>
@@ -3017,9 +3008,6 @@
       <c r="AA8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
       <c r="AI8" s="1" t="s">
         <v>95</v>
       </c>
